--- a/buildplan_generator/output/25-074 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-074 GENERATED BUILD PLAN.xlsx
@@ -74,12 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -88,6 +82,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 23-040, 25-054, 23-020</t>
+          <t>25-054, 23-004, 23-005, 23-027, 23-031</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -689,8 +687,8 @@
       <c r="E8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="10" t="n">
-        <v>4.5</v>
+      <c r="F8" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
@@ -699,7 +697,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>3.0-7.0</t>
+          <t>ratio=1.07 (0.86-1.50)</t>
         </is>
       </c>
       <c r="I8" s="8" t="n"/>
@@ -726,8 +724,8 @@
       <c r="E9" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>8</v>
+      <c r="F9" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -736,7 +734,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>6.5-15.0</t>
+          <t>ratio=1.00 (0.50-1.11)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -763,8 +761,8 @@
       <c r="E10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>1</v>
+      <c r="F10" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -773,7 +771,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -800,8 +798,8 @@
       <c r="E11" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>1.5</v>
+      <c r="F11" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -810,7 +808,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -837,7 +835,7 @@
       <c r="E12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -847,7 +845,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -874,8 +872,8 @@
       <c r="E13" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>4</v>
+      <c r="F13" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -884,7 +882,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>4.0-10.0</t>
+          <t>ratio=1.00 (0.75-1.50)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -911,7 +909,7 @@
       <c r="E14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="9" t="n">
         <v>3</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -921,7 +919,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=1.50 (0.62-1.75)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -965,8 +963,8 @@
       <c r="E16" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>37.5</v>
+      <c r="F16" s="9" t="n">
+        <v>28.9</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -975,7 +973,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>22.5-62.2</t>
+          <t>ratio=1.20 (1.04-2.19)</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1003,16 +1001,16 @@
         <v>16</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>3.5-20.2</t>
+          <t>ratio=1.12 (n=1)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1056,8 +1054,8 @@
       <c r="E19" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>3.5</v>
+      <c r="F19" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1066,7 +1064,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>2.0-26.0</t>
+          <t>ratio=1.00 (0.93-1.62)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1093,8 +1091,8 @@
       <c r="E20" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="10" t="n">
-        <v>2.5</v>
+      <c r="F20" s="9" t="n">
+        <v>6.4</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1103,7 +1101,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=1.06 (0.50-1.12)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1147,7 +1145,7 @@
       <c r="E22" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -1157,7 +1155,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1184,7 +1182,7 @@
       <c r="E23" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="11" t="n">
         <v>4</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -1194,7 +1192,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>global:4.0-4.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1221,8 +1219,8 @@
       <c r="E24" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="9" t="n">
-        <v>2</v>
+      <c r="F24" s="11" t="n">
+        <v>5</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1231,7 +1229,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-6.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1258,8 +1256,8 @@
       <c r="E25" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="9" t="n">
-        <v>3</v>
+      <c r="F25" s="11" t="n">
+        <v>4</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1268,7 +1266,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>global:1.2-6.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1295,8 +1293,8 @@
       <c r="E26" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F26" s="9" t="n">
-        <v>8</v>
+      <c r="F26" s="11" t="n">
+        <v>16</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1305,7 +1303,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-32.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1332,8 +1330,8 @@
       <c r="E27" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F27" s="9" t="n">
-        <v>1</v>
+      <c r="F27" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1342,7 +1340,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-54.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1386,7 +1384,7 @@
       <c r="E29" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" s="10" t="n">
         <v>2</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -1396,7 +1394,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1424,12 +1422,12 @@
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1456,8 +1454,8 @@
       <c r="E31" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>20</v>
+      <c r="F31" s="9" t="n">
+        <v>22.2</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1466,7 +1464,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>5.0-27.0</t>
+          <t>ratio=1.11 (1.06-1.80)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1493,8 +1491,8 @@
       <c r="E32" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>15</v>
+      <c r="F32" s="9" t="n">
+        <v>26</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1501,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>4.0-20.0</t>
+          <t>ratio=1.08 (0.96-1.33)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1545,17 +1543,15 @@
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
-      <c r="F34" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1582,8 +1578,8 @@
       <c r="E35" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>4.2</v>
+      <c r="F35" s="9" t="n">
+        <v>1.7</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1592,7 +1588,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>2.0-12.5</t>
+          <t>ratio=1.70 (1.40-2.40)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1619,8 +1615,8 @@
       <c r="E36" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>2</v>
+      <c r="F36" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1629,7 +1625,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.50 (1.25-1.56)</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1656,8 +1652,8 @@
       <c r="E37" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>6</v>
+      <c r="F37" s="9" t="n">
+        <v>9.5</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1666,7 +1662,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
+          <t>ratio=1.19 (1.00-1.50)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1710,8 +1706,8 @@
       <c r="E39" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="9" t="n">
-        <v>2</v>
+      <c r="F39" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1720,7 +1716,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-26.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1747,7 +1743,7 @@
       <c r="E40" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -1757,7 +1753,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-7.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1785,16 +1781,16 @@
         <v>2</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>1.5-1.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1838,8 +1834,8 @@
       <c r="E43" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>15.5</v>
+      <c r="F43" s="9" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1848,7 +1844,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>6.5-20.0</t>
+          <t>ratio=1.21 (0.83-2.29)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1875,8 +1871,8 @@
       <c r="E44" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>15</v>
+      <c r="F44" s="9" t="n">
+        <v>19.5</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1885,7 +1881,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>4.0-20.2</t>
+          <t>ratio=1.62 (0.50-2.06)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1912,8 +1908,8 @@
       <c r="E45" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>13.5</v>
+      <c r="F45" s="9" t="n">
+        <v>22.5</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1922,7 +1918,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>5.0-17.0</t>
+          <t>ratio=1.25 (0.83-2.50)</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1949,8 +1945,8 @@
       <c r="E46" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>4</v>
+      <c r="F46" s="9" t="n">
+        <v>5.8</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1959,7 +1955,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=0.83 (0.27-1.17)</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1986,8 +1982,8 @@
       <c r="E47" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F47" s="9" t="n">
-        <v>6</v>
+      <c r="F47" s="11" t="n">
+        <v>25.8</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1996,7 +1992,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>global:2.5-31.5</t>
+          <t>wc_ratio=1.29</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2021,17 +2017,15 @@
         </is>
       </c>
       <c r="E48" s="8" t="n"/>
-      <c r="F48" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2058,8 +2052,8 @@
       <c r="E49" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F49" s="10" t="n">
-        <v>9</v>
+      <c r="F49" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2068,7 +2062,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>4.5-13.0</t>
+          <t>ratio=1.00 (0.86-1.29)</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2095,8 +2089,8 @@
       <c r="E50" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F50" s="11" t="n">
-        <v>3.5</v>
+      <c r="F50" s="10" t="n">
+        <v>4.7</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2105,7 +2099,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>3.5-3.5</t>
+          <t>ratio=0.29 (n=1)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2132,8 +2126,8 @@
       <c r="E51" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F51" s="10" t="n">
-        <v>16.8</v>
+      <c r="F51" s="9" t="n">
+        <v>36</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2142,7 +2136,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>12.0-22.0</t>
+          <t>ratio=1.50 (1.22-2.00)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2169,8 +2163,8 @@
       <c r="E52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F52" s="10" t="n">
-        <v>3</v>
+      <c r="F52" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2179,7 +2173,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>2.0-12.0</t>
+          <t>ratio=1.50 (0.50-2.00)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2223,8 +2217,8 @@
       <c r="E54" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="F54" s="10" t="n">
-        <v>19.5</v>
+      <c r="F54" s="9" t="n">
+        <v>27</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2233,7 +2227,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>10.0-36.5</t>
+          <t>ratio=0.84 (0.81-0.98)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2260,8 +2254,8 @@
       <c r="E55" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F55" s="10" t="n">
-        <v>3</v>
+      <c r="F55" s="9" t="n">
+        <v>19.4</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2270,7 +2264,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>2.5-15.5</t>
+          <t>ratio=1.21 (0.60-2.07)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2297,8 +2291,8 @@
       <c r="E56" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F56" s="10" t="n">
-        <v>7</v>
+      <c r="F56" s="9" t="n">
+        <v>19.3</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2307,7 +2301,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>7.0-32.0</t>
+          <t>ratio=0.81 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2334,17 +2328,17 @@
       <c r="E57" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F57" s="11" t="n">
-        <v>10</v>
+      <c r="F57" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>10.0-10.0</t>
+          <t>ratio=1.00 (0.83-2.75)</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2369,17 +2363,15 @@
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
-      <c r="F58" s="9" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2406,7 +2398,7 @@
       <c r="E59" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="10" t="n">
+      <c r="F59" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -2416,7 +2408,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.00 (1.00-2.25)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2465,12 +2457,12 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=1.50 (n=1)</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2495,17 +2487,15 @@
         </is>
       </c>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="11" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>1.5-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2549,8 +2539,8 @@
       <c r="E64" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F64" s="10" t="n">
-        <v>2</v>
+      <c r="F64" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2559,7 +2549,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>1.0-17.0</t>
+          <t>ratio=5.00 (0.50-5.00)</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2586,8 +2576,8 @@
       <c r="E65" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F65" s="10" t="n">
-        <v>15.5</v>
+      <c r="F65" s="9" t="n">
+        <v>21</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2596,7 +2586,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>9.0-33.0</t>
+          <t>ratio=1.05 (0.46-2.75)</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2624,12 +2614,12 @@
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2656,8 +2646,8 @@
       <c r="E67" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="F67" s="10" t="n">
-        <v>75.5</v>
+      <c r="F67" s="9" t="n">
+        <v>97.2</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2666,7 +2656,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>25.5-96.2</t>
+          <t>ratio=1.94 (1.34-2.41)</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2694,12 +2684,12 @@
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2743,8 +2733,8 @@
       <c r="E70" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F70" s="10" t="n">
-        <v>6.5</v>
+      <c r="F70" s="9" t="n">
+        <v>12.8</v>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
@@ -2753,7 +2743,7 @@
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>1.5-11.8</t>
+          <t>ratio=3.21 (1.50-5.00)</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2781,12 +2771,12 @@
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2813,8 +2803,8 @@
       <c r="E72" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F72" s="10" t="n">
-        <v>11.8</v>
+      <c r="F72" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
@@ -2823,7 +2813,7 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>7.0-17.0</t>
+          <t>ratio=1.50 (0.93-3.50)</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2837,7 +2827,7 @@
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>392.5</v>
+        <v>586.7</v>
       </c>
     </row>
   </sheetData>
@@ -2905,7 +2895,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 23-040, 25-054, 23-020</t>
+          <t>25-054, 23-004, 23-005, 23-027, 23-031</t>
         </is>
       </c>
     </row>
@@ -4681,35 +4671,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-073</t>
+          <t>25-054</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-072</t>
+          <t>23-004</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-040</t>
+          <t>23-005</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-054</t>
+          <t>23-027</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-020</t>
+          <t>23-031</t>
         </is>
       </c>
     </row>
@@ -4764,23 +4754,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4794,7 +4780,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4803,12 +4789,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.0-7.0</t>
+          <t>ratio=1.07 (0.86-1.50)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4810,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4833,12 +4819,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6.5-15.0</t>
+          <t>ratio=1.00 (0.50-1.11)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4840,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4863,12 +4849,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4870,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4893,12 +4879,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4909,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4930,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4953,12 +4939,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4.0-10.0</t>
+          <t>ratio=1.00 (0.75-1.50)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -4983,12 +4969,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=1.50 (0.62-1.75)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5004,7 +4990,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37.5</v>
+        <v>28.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5013,12 +4999,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22.5-62.2</t>
+          <t>ratio=1.20 (1.04-2.19)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5034,21 +5020,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.5-20.2</t>
+          <t>ratio=1.12 (n=1)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054</t>
+          <t>25-054</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5050,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.5</v>
+        <v>20</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5073,12 +5059,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.0-26.0</t>
+          <t>ratio=1.00 (0.93-1.62)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5080,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5103,12 +5089,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=1.06 (0.50-1.12)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 23-040, 23-020</t>
+          <t>23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5133,12 +5119,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5149,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>global:4.0-4.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5170,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5193,12 +5179,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>global:1.0-6.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5200,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5223,12 +5209,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>global:1.2-6.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5230,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5253,12 +5239,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>global:0.5-32.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5260,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5283,12 +5269,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>global:0.5-54.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5299,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5338,19 +5324,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>23-020, 23-040, 25-054, 25-072, 25-073</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5364,7 +5346,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5373,12 +5355,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.0-27.0</t>
+          <t>ratio=1.11 (1.06-1.80)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5376,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5403,12 +5385,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4.0-20.0</t>
+          <t>ratio=1.08 (0.96-1.33)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5424,23 +5406,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5454,7 +5432,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5463,12 +5441,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.0-12.5</t>
+          <t>ratio=1.70 (1.40-2.40)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 23-040, 23-020</t>
+          <t>23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5462,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5493,12 +5471,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.50 (1.25-1.56)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 23-040, 23-020</t>
+          <t>23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5492,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5523,12 +5501,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
+          <t>ratio=1.19 (1.00-1.50)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 23-040, 23-020</t>
+          <t>23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5544,23 +5522,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5574,7 +5548,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5583,12 +5557,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>global:0.5-26.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5587,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>global:0.5-7.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5634,21 +5608,21 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5-1.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>23-040</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5638,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>15.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5673,12 +5647,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.5-20.0</t>
+          <t>ratio=1.21 (0.83-2.29)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5668,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5703,12 +5677,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.0-20.2</t>
+          <t>ratio=1.62 (0.50-2.06)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5698,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>13.5</v>
+        <v>22.5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5733,12 +5707,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.0-17.0</t>
+          <t>ratio=1.25 (0.83-2.50)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5728,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5763,12 +5737,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=0.83 (0.27-1.17)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5784,23 +5758,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5814,7 +5784,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5823,12 +5793,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4.5-13.0</t>
+          <t>ratio=1.00 (0.86-1.29)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5814,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5853,7 +5823,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3.5-3.5</t>
+          <t>ratio=0.29 (n=1)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5874,7 +5844,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16.8</v>
+        <v>36</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5883,12 +5853,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12.0-22.0</t>
+          <t>ratio=1.50 (1.22-2.00)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5874,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5913,12 +5883,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2.0-12.0</t>
+          <t>ratio=1.50 (0.50-2.00)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5904,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5943,12 +5913,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>10.0-36.5</t>
+          <t>ratio=0.84 (0.81-0.98)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5934,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>19.4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5973,12 +5943,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2.5-15.5</t>
+          <t>ratio=1.21 (0.60-2.07)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5964,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>19.3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6003,12 +5973,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.0-32.0</t>
+          <t>ratio=0.81 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -6024,21 +5994,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>10.0-10.0</t>
+          <t>ratio=1.00 (0.83-2.75)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>23-020</t>
+          <t>23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -6054,23 +6024,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>global:0.5-2.0</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6093,12 +6059,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.00 (1.00-2.25)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -6118,17 +6084,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=1.50 (n=1)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>23-031</t>
         </is>
       </c>
     </row>
@@ -6144,23 +6110,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.5-1.5</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6174,7 +6136,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6183,12 +6145,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.0-17.0</t>
+          <t>ratio=5.00 (0.50-5.00)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6166,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6213,12 +6175,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>9.0-33.0</t>
+          <t>ratio=1.05 (0.46-2.75)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -6238,19 +6200,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>23-020, 23-040, 25-054, 25-072, 25-073</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6264,7 +6222,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>75.5</v>
+        <v>97.2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6273,12 +6231,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.5-96.2</t>
+          <t>ratio=1.94 (1.34-2.41)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -6298,19 +6256,15 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>23-020, 23-040, 25-054, 25-072, 25-073</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6324,7 +6278,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6.5</v>
+        <v>12.8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6333,12 +6287,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.5-11.8</t>
+          <t>ratio=3.21 (1.50-5.00)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005</t>
         </is>
       </c>
     </row>
@@ -6358,19 +6312,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>23-020, 23-040, 25-054, 25-072, 25-073</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6384,7 +6334,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>11.8</v>
+        <v>9</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6393,12 +6343,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7.0-17.0</t>
+          <t>ratio=1.50 (0.93-3.50)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>25-073, 25-072, 25-054, 23-040, 23-020</t>
+          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6364,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>25.8</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6423,12 +6373,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>global:2.5-31.5</t>
+          <t>wc_ratio=1.29</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-074 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-074 GENERATED BUILD PLAN.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-054, 23-004, 23-005, 23-027, 23-031</t>
+          <t>25-054, 23-027, 23-031, 23-004, 23-005</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-054, 23-004, 23-005, 23-027, 23-031</t>
+          <t>25-054, 23-027, 23-031, 23-004, 23-005</t>
         </is>
       </c>
     </row>
@@ -4678,28 +4678,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-004</t>
+          <t>23-027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-005</t>
+          <t>23-031</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-027</t>
+          <t>23-004</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-031</t>
+          <t>23-005</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-074 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-074 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,12 +76,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -638,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -688,7 +681,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>4.3</v>
+        <v>7.7</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
@@ -697,7 +690,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.07 (0.86-1.50)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="I8" s="8" t="n"/>
@@ -725,7 +718,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>10</v>
+        <v>16.2</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -734,7 +727,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.11)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -762,7 +755,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -771,7 +764,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -799,7 +792,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -808,7 +801,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.50)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -836,7 +829,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -845,7 +838,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -873,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -882,7 +875,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.50)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -910,7 +903,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -919,7 +912,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.62-1.75)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -964,7 +957,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>28.9</v>
+        <v>37</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -973,7 +966,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.20 (1.04-2.19)</t>
+          <t>group_total:46h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1000,17 +993,17 @@
       <c r="E17" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>18</v>
+      <c r="F17" s="9" t="n">
+        <v>8.6</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (n=1)</t>
+          <t>group_total:46h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1055,7 +1048,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>20</v>
+        <v>35.7</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1064,7 +1057,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.93-1.62)</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1092,7 +1085,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1101,7 +1094,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.06 (0.50-1.12)</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1146,7 +1139,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1155,7 +1148,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1182,17 +1175,17 @@
       <c r="E23" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>4</v>
+      <c r="F23" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1219,17 +1212,17 @@
       <c r="E24" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>5</v>
+      <c r="F24" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1256,17 +1249,17 @@
       <c r="E25" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="11" t="n">
-        <v>4</v>
+      <c r="F25" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1293,17 +1286,17 @@
       <c r="E26" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F26" s="11" t="n">
-        <v>16</v>
+      <c r="F26" s="9" t="n">
+        <v>7.2</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1330,17 +1323,17 @@
       <c r="E27" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F27" s="11" t="n">
-        <v>8</v>
+      <c r="F27" s="9" t="n">
+        <v>12.5</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1384,17 +1377,17 @@
       <c r="E29" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>2</v>
+      <c r="F29" s="9" t="n">
+        <v>0.7</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1422,12 +1415,12 @@
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1455,7 +1448,7 @@
         <v>20</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>22.2</v>
+        <v>17.3</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1464,7 +1457,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.11 (1.06-1.80)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1492,7 +1485,7 @@
         <v>24</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1501,7 +1494,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.08 (0.96-1.33)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1546,12 +1539,12 @@
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1579,7 +1572,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1588,7 +1581,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.70 (1.40-2.40)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1616,7 +1609,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1625,7 +1618,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.25-1.56)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1653,7 +1646,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1662,7 +1655,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.19 (1.00-1.50)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1706,17 +1699,17 @@
       <c r="E39" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="11" t="n">
-        <v>1</v>
+      <c r="F39" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1743,17 +1736,17 @@
       <c r="E40" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="11" t="n">
-        <v>1</v>
+      <c r="F40" s="9" t="n">
+        <v>1.6</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1780,17 +1773,17 @@
       <c r="E41" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="11" t="n">
-        <v>2</v>
+      <c r="F41" s="9" t="n">
+        <v>3.1</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1835,7 +1828,7 @@
         <v>8</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>9.699999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1844,7 +1837,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.21 (0.83-2.29)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1872,7 +1865,7 @@
         <v>12</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>19.5</v>
+        <v>10.1</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1881,7 +1874,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.62 (0.50-2.06)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1909,7 +1902,7 @@
         <v>18</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>22.5</v>
+        <v>11.9</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1918,7 +1911,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.83-2.50)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1946,7 +1939,7 @@
         <v>7</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1955,7 +1948,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.27-1.17)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1982,17 +1975,17 @@
       <c r="E47" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F47" s="11" t="n">
-        <v>25.8</v>
+      <c r="F47" s="9" t="n">
+        <v>3.8</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.29</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2020,12 +2013,12 @@
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2053,7 +2046,7 @@
         <v>8</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>8</v>
+        <v>10.4</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2062,7 +2055,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.86-1.29)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2089,17 +2082,17 @@
       <c r="E50" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F50" s="10" t="n">
-        <v>4.7</v>
+      <c r="F50" s="9" t="n">
+        <v>5.3</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.29 (n=1)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2127,7 +2120,7 @@
         <v>24</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>36</v>
+        <v>24.2</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2136,7 +2129,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.22-2.00)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2163,17 +2156,17 @@
       <c r="E52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F52" s="9" t="n">
-        <v>4.5</v>
+      <c r="F52" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.50-2.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2218,7 +2211,7 @@
         <v>32</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2227,7 +2220,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.84 (0.81-0.98)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2255,7 +2248,7 @@
         <v>16</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>19.4</v>
+        <v>14.5</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2264,7 +2257,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.21 (0.60-2.07)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2292,7 +2285,7 @@
         <v>24</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>19.3</v>
+        <v>28.8</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2301,7 +2294,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.81 (0.50-1.50)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2329,7 +2322,7 @@
         <v>12</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>12</v>
+        <v>6.9</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2338,7 +2331,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-2.75)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2366,12 +2359,12 @@
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2399,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2408,7 +2401,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.25)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2452,17 +2445,17 @@
       <c r="E61" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="10" t="n">
-        <v>3</v>
+      <c r="F61" s="9" t="n">
+        <v>3.2</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=1)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2490,12 +2483,12 @@
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2540,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>15</v>
+        <v>6.7</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2549,7 +2542,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>ratio=5.00 (0.50-5.00)</t>
+          <t>group_total:117h</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2577,7 +2570,7 @@
         <v>20</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>21</v>
+        <v>31.9</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2586,7 +2579,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.05 (0.46-2.75)</t>
+          <t>group_total:117h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2614,12 +2607,12 @@
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2647,7 +2640,7 @@
         <v>50</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>97.2</v>
+        <v>55</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2656,7 +2649,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.94 (1.34-2.41)</t>
+          <t>group_total:117h</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2684,12 +2677,12 @@
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2734,7 +2727,7 @@
         <v>4</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
@@ -2743,7 +2736,7 @@
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.21 (1.50-5.00)</t>
+          <t>group_total:117h</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2771,12 +2764,12 @@
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2804,7 +2797,7 @@
         <v>6</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>9</v>
+        <v>13.3</v>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
@@ -2813,7 +2806,7 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.93-3.50)</t>
+          <t>group_total:117h</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2827,7 +2820,7 @@
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>586.7</v>
+        <v>505.5</v>
       </c>
     </row>
   </sheetData>
@@ -4758,15 +4751,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4780,7 +4777,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.3</v>
+        <v>7.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4789,12 +4786,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ratio=1.07 (0.86-1.50)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4807,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>16.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4819,12 +4816,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.11)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4837,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4849,12 +4846,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4867,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4879,12 +4876,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.50)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4897,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4909,12 +4906,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4927,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4939,12 +4936,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.50)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4957,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4969,12 +4966,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.62-1.75)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4987,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>28.9</v>
+        <v>37</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4999,12 +4996,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.20 (1.04-2.19)</t>
+          <t>group_total:46h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5020,21 +5017,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.12 (n=1)</t>
+          <t>group_total:46h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-054</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5047,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>35.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5059,12 +5056,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.93-1.62)</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5077,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5089,12 +5086,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=1.06 (0.50-1.12)</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>23-031, 23-027, 23-005, 23-004</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5107,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5119,12 +5116,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5140,21 +5137,21 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5170,21 +5167,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5200,21 +5197,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5230,21 +5227,21 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>7.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5260,21 +5257,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5290,21 +5287,21 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-054</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5324,15 +5321,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5346,7 +5347,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>22.2</v>
+        <v>17.3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5355,12 +5356,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.11 (1.06-1.80)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5377,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5385,12 +5386,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=1.08 (0.96-1.33)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5410,15 +5411,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5432,7 +5437,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5441,12 +5446,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.70 (1.40-2.40)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>23-031, 23-027, 23-005, 23-004</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5467,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5471,12 +5476,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.25-1.56)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>23-031, 23-027, 23-005, 23-004</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5497,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5501,12 +5506,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=1.19 (1.00-1.50)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>23-031, 23-027, 23-005, 23-004</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5526,15 +5531,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5548,21 +5557,21 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5578,21 +5587,21 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5608,21 +5617,21 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5647,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9.699999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5647,12 +5656,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=1.21 (0.83-2.29)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5677,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>19.5</v>
+        <v>10.1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5677,12 +5686,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=1.62 (0.50-2.06)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5707,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>22.5</v>
+        <v>11.9</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5707,12 +5716,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.83-2.50)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5737,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5737,12 +5746,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.27-1.17)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5762,15 +5771,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5784,7 +5797,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>10.4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5793,12 +5806,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.86-1.29)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5814,21 +5827,21 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=0.29 (n=1)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-054</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5857,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>36</v>
+        <v>24.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5853,12 +5866,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.22-2.00)</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5874,21 +5887,21 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.50-2.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5917,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5913,12 +5926,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=0.84 (0.81-0.98)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5947,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>19.4</v>
+        <v>14.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5943,12 +5956,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=1.21 (0.60-2.07)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5977,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>19.3</v>
+        <v>28.8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5973,12 +5986,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=0.81 (0.50-1.50)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5994,7 +6007,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>6.9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6003,12 +6016,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-2.75)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>23-031, 23-027, 23-005, 23-004</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6028,15 +6041,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6050,7 +6067,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6059,12 +6076,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.25)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6080,21 +6097,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=1)</t>
+          <t>group_total:84h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>23-031</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6114,15 +6131,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6136,7 +6157,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>15</v>
+        <v>6.7</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6145,12 +6166,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ratio=5.00 (0.50-5.00)</t>
+          <t>group_total:117h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6187,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>21</v>
+        <v>31.9</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6175,12 +6196,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ratio=1.05 (0.46-2.75)</t>
+          <t>group_total:117h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6200,15 +6221,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6222,7 +6247,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>97.2</v>
+        <v>55</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6231,12 +6256,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ratio=1.94 (1.34-2.41)</t>
+          <t>group_total:117h</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6256,15 +6281,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6278,7 +6307,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6287,12 +6316,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ratio=3.21 (1.50-5.00)</t>
+          <t>group_total:117h</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6312,15 +6341,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6334,7 +6367,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>13.3</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6343,12 +6376,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.93-3.50)</t>
+          <t>group_total:117h</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>25-054, 23-031, 23-027, 23-005, 23-004</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6364,21 +6397,21 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>25.8</v>
+        <v>3.8</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>wc_ratio=1.29</t>
+          <t>group_total:87h</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-074 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-074 GENERATED BUILD PLAN.xlsx
@@ -681,7 +681,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I8" s="8" t="n"/>
@@ -718,7 +718,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -755,7 +755,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -866,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -903,7 +903,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -957,7 +957,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>37</v>
+        <v>33.9</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>group_total:46h</t>
+          <t>group_total:42h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -994,7 +994,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>group_total:46h</t>
+          <t>group_total:42h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1048,7 +1048,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>35.7</v>
+        <v>36.6</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>group_total:41h</t>
+          <t>group_total:42h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1085,7 +1085,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>group_total:41h</t>
+          <t>group_total:42h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1139,7 +1139,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1176,7 +1176,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1213,7 +1213,7 @@
         <v>5</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1250,7 +1250,7 @@
         <v>4</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1287,7 +1287,7 @@
         <v>16</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1324,7 +1324,7 @@
         <v>8</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1378,7 +1378,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1448,7 +1448,7 @@
         <v>20</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>17.3</v>
+        <v>13.9</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1485,7 +1485,7 @@
         <v>24</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>16</v>
+        <v>12.9</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1572,7 +1572,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1609,7 +1609,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1646,7 +1646,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1700,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1737,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1774,7 +1774,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1828,7 +1828,7 @@
         <v>8</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1865,7 +1865,7 @@
         <v>12</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1902,7 +1902,7 @@
         <v>18</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1939,7 +1939,7 @@
         <v>7</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1976,7 +1976,7 @@
         <v>20</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2046,7 +2046,7 @@
         <v>8</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2083,7 +2083,7 @@
         <v>16</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2120,7 +2120,7 @@
         <v>24</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2211,7 +2211,7 @@
         <v>32</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>29</v>
+        <v>24.4</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2248,7 +2248,7 @@
         <v>16</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>14.5</v>
+        <v>12.2</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2285,7 +2285,7 @@
         <v>24</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>28.8</v>
+        <v>24.3</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2322,7 +2322,7 @@
         <v>12</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2392,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2446,7 +2446,7 @@
         <v>2</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2533,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>group_total:117h</t>
+          <t>group_total:112h</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2570,7 +2570,7 @@
         <v>20</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>31.9</v>
+        <v>30.5</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>group_total:117h</t>
+          <t>group_total:112h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2640,7 +2640,7 @@
         <v>50</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>55</v>
+        <v>52.7</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>group_total:117h</t>
+          <t>group_total:112h</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2727,7 +2727,7 @@
         <v>4</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>group_total:117h</t>
+          <t>group_total:112h</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2797,7 +2797,7 @@
         <v>6</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>13.3</v>
+        <v>12.7</v>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>group_total:117h</t>
+          <t>group_total:112h</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>505.5</v>
+        <v>471.6</v>
       </c>
     </row>
   </sheetData>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37</v>
+        <v>33.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:46h</t>
+          <t>group_total:42h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>group_total:46h</t>
+          <t>group_total:42h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35.7</v>
+        <v>36.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:41h</t>
+          <t>group_total:42h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:41h</t>
+          <t>group_total:42h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:29h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17.3</v>
+        <v>13.9</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16</v>
+        <v>12.9</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>29</v>
+        <v>24.4</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>14.5</v>
+        <v>12.2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>28.8</v>
+        <v>24.3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>group_total:84h</t>
+          <t>group_total:71h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>group_total:117h</t>
+          <t>group_total:112h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>31.9</v>
+        <v>30.5</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>group_total:117h</t>
+          <t>group_total:112h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>55</v>
+        <v>52.7</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>group_total:117h</t>
+          <t>group_total:112h</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>group_total:117h</t>
+          <t>group_total:112h</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>13.3</v>
+        <v>12.7</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>group_total:117h</t>
+          <t>group_total:112h</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>group_total:87h</t>
+          <t>group_total:86h</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
